--- a/diseases/d043/2005-2009.xlsx
+++ b/diseases/d043/2005-2009.xlsx
@@ -439,110 +439,255 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>record_kind</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>country_code</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>country_name</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>disease_id</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>disease_name_en</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>disease_name_zh</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>year_month</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
         <is>
           <t>cases</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>weekly_equiv_cases</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>deaths</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>incidence_rate_per_100k</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>incidence_rate_source</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>mortality_rate</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>series_code</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>source_series_code</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>source_system</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>source_label</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>metric_type</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>reporting_basis</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>temporal_granularity</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>geography_key</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>dimension_key</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>mapping_relation</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>comparability</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>aggregation_policy</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>availability_status</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>missing_value_policy</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>definition_version</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>case_definition</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>case_definition_uri</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>quality_status</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>is_selected_series</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>data_layer</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>projection_policy</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>coverage_status</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>loss_risk</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>selected_series_codes</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>available_series_count</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>provenance_note</t>
+        </is>
+      </c>
+      <c r="AV1" t="inlineStr">
         <is>
           <t>primary_source_scope</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>primary_source_label</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>primary_source_url</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>primary_source_type</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>source_scopes</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>source_labels</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>source_urls</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>source_types</t>
         </is>
@@ -571,97 +716,126 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>HK</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>Hong Kong, China</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>D043</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>Typhus</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>流行性和地方性斑疹伤寒</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>2009-01-01</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>2009-01</t>
         </is>
       </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
       <c r="N2" t="n">
         <v>0</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
       </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AW2" t="inlineStr">
         <is>
           <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AX2" t="inlineStr">
         <is>
           <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AY2" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="AZ2" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="BA2" t="inlineStr">
         <is>
           <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="BB2" t="inlineStr">
         <is>
           <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="BC2" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
@@ -690,97 +864,126 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>HK</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>Hong Kong, China</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>D043</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>Typhus</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>流行性和地方性斑疹伤寒</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>2009-02-01</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>2009-02</t>
         </is>
       </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
       <c r="N3" t="n">
         <v>0</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
       </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="inlineStr">
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="AW3" t="inlineStr">
         <is>
           <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="AY3" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="AZ3" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="BA3" t="inlineStr">
         <is>
           <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="BB3" t="inlineStr">
         <is>
           <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="BC3" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
@@ -809,97 +1012,126 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>HK</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>Hong Kong, China</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>D043</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>Typhus</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>流行性和地方性斑疹伤寒</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>2009-03-01</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>2009-03</t>
         </is>
       </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
       <c r="N4" t="n">
         <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
       </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="inlineStr">
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="AW4" t="inlineStr">
         <is>
           <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="AY4" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="AZ4" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="BA4" t="inlineStr">
         <is>
           <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="BB4" t="inlineStr">
         <is>
           <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="BC4" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
@@ -928,97 +1160,126 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>HK</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>Hong Kong, China</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>D043</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>Typhus</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>流行性和地方性斑疹伤寒</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>2009-04-01</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>2009-04</t>
         </is>
       </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="inlineStr">
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="AW5" t="inlineStr">
         <is>
           <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="AY5" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="AZ5" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="BA5" t="inlineStr">
         <is>
           <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="BB5" t="inlineStr">
         <is>
           <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="BC5" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
@@ -1047,97 +1308,126 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>HK</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>Hong Kong, China</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>D043</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>Typhus</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>流行性和地方性斑疹伤寒</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>2009-05-01</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>2009-05</t>
         </is>
       </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
       </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="inlineStr">
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="AW6" t="inlineStr">
         <is>
           <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="AX6" t="inlineStr">
         <is>
           <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="AY6" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="AZ6" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="BA6" t="inlineStr">
         <is>
           <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="BB6" t="inlineStr">
         <is>
           <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="BC6" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
@@ -1166,97 +1456,126 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>HK</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>Hong Kong, China</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>D043</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>Typhus</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>流行性和地方性斑疹伤寒</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>2009-06-01</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>2009-06</t>
         </is>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>1</v>
       </c>
-      <c r="N7" t="n">
-        <v>0.2258064516129032</v>
-      </c>
       <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
         <v>0.01415535058450628</v>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr"/>
+      <c r="AT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="AW7" t="inlineStr">
         <is>
           <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="AX7" t="inlineStr">
         <is>
           <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="AY7" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="AZ7" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="BA7" t="inlineStr">
         <is>
           <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="BB7" t="inlineStr">
         <is>
           <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="BC7" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
@@ -1285,97 +1604,126 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t>HK</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>Hong Kong, China</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>D043</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>Typhus</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>流行性和地方性斑疹伤寒</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>2009-07-01</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>2009-07</t>
         </is>
       </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
       </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="AW8" t="inlineStr">
         <is>
           <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="AX8" t="inlineStr">
         <is>
           <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="AY8" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="AZ8" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="BA8" t="inlineStr">
         <is>
           <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="BB8" t="inlineStr">
         <is>
           <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="BC8" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
@@ -1404,97 +1752,126 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t>HK</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>Hong Kong, China</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>D043</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>Typhus</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>流行性和地方性斑疹伤寒</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>2009-08-01</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>2009-08</t>
         </is>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>1</v>
       </c>
-      <c r="N9" t="n">
-        <v>0.2258064516129032</v>
-      </c>
       <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
         <v>0.01415535058450628</v>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr"/>
+      <c r="AT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="AW9" t="inlineStr">
         <is>
           <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="AX9" t="inlineStr">
         <is>
           <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="AY9" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="AZ9" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="BA9" t="inlineStr">
         <is>
           <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="BB9" t="inlineStr">
         <is>
           <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="BC9" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
@@ -1523,97 +1900,126 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t>HK</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>Hong Kong, China</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>D043</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>Typhus</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>流行性和地方性斑疹伤寒</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>2009-09-01</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>2009-09</t>
         </is>
       </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
       </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="inlineStr">
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr"/>
+      <c r="AT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="AW10" t="inlineStr">
         <is>
           <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="AX10" t="inlineStr">
         <is>
           <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="AY10" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="AZ10" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="BA10" t="inlineStr">
         <is>
           <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
+      <c r="BB10" t="inlineStr">
         <is>
           <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="BC10" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
@@ -1642,97 +2048,126 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t>HK</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>Hong Kong, China</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>D043</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>Typhus</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>流行性和地方性斑疹伤寒</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>2009-10-01</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>2009-10</t>
         </is>
       </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
       </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="inlineStr">
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr"/>
+      <c r="AT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="AW11" t="inlineStr">
         <is>
           <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="AX11" t="inlineStr">
         <is>
           <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="AY11" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="AZ11" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="BA11" t="inlineStr">
         <is>
           <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
+      <c r="BB11" t="inlineStr">
         <is>
           <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="BC11" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
@@ -1761,97 +2196,126 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
           <t>HK</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>Hong Kong, China</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>D043</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>Typhus</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>流行性和地方性斑疹伤寒</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>2009-11-01</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>2009-11</t>
         </is>
       </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
       </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="inlineStr">
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr"/>
+      <c r="AT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV12" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="AW12" t="inlineStr">
         <is>
           <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="AX12" t="inlineStr">
         <is>
           <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="AY12" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="AZ12" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="BA12" t="inlineStr">
         <is>
           <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
+      <c r="BB12" t="inlineStr">
         <is>
           <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="BC12" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
@@ -1880,97 +2344,126 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
           <t>HK</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>Hong Kong, China</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>D043</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>Typhus</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>流行性和地方性斑疹伤寒</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>2009-12-01</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>2009-12</t>
         </is>
       </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
       </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="inlineStr">
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr"/>
+      <c r="AT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV13" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="AW13" t="inlineStr">
         <is>
           <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="AX13" t="inlineStr">
         <is>
           <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="AY13" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="AZ13" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
+      <c r="BA13" t="inlineStr">
         <is>
           <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
+      <c r="BB13" t="inlineStr">
         <is>
           <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
+      <c r="BC13" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
@@ -2088,7 +2581,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>record_count</t>
+          <t>projection_record_count</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -2098,27 +2591,27 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>schema_version</t>
+          <t>record_count</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>total_cases</t>
+          <t>schema_version</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>total_deaths</t>
+          <t>source_observation_count</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -2128,22 +2621,64 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>window_end</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2009-12-31</t>
-        </is>
+          <t>source_series_count</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>total_basis</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>total_cases</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>total_deaths</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>window_end</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2009-12-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>window_start</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>2005-01-01</t>
         </is>
